--- a/task130/target/ta_weekly_position_2026-09-28.xlsx
+++ b/task130/target/ta_weekly_position_2026-09-28.xlsx
@@ -435,15 +435,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -456,7 +457,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Households in TA at midnight on Sunday 27 September, by accommodation type and bedrooms needed.</t>
+          <t>Households in TA at midnight on Sunday 27 September, by accommodation type and the size of the unit they occupy (bed and breakfast and hostel households by room).</t>
         </is>
       </c>
     </row>
@@ -469,25 +470,30 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>1 bed</t>
+          <t>1 bed unit</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>2 bed</t>
+          <t>2 bed unit</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>3 bed</t>
+          <t>3 bed unit</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>4+ bed</t>
+          <t>4 bed unit</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Room</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>All</t>
         </is>
@@ -500,19 +506,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>52</v>
+        <v>225</v>
+      </c>
+      <c r="G5" t="n">
+        <v>225</v>
       </c>
     </row>
     <row r="6">
@@ -522,19 +531,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>23</v>
+        <v>168</v>
+      </c>
+      <c r="G6" t="n">
+        <v>168</v>
       </c>
     </row>
     <row r="7">
@@ -544,19 +556,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="C7" t="n">
-        <v>152</v>
+        <v>130</v>
       </c>
       <c r="D7" t="n">
-        <v>198</v>
+        <v>228</v>
       </c>
       <c r="E7" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="F7" t="n">
-        <v>669</v>
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>706</v>
       </c>
     </row>
     <row r="8">
@@ -566,19 +581,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="C8" t="n">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D8" t="n">
-        <v>189</v>
+        <v>217</v>
       </c>
       <c r="E8" t="n">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="F8" t="n">
-        <v>692</v>
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>683</v>
       </c>
     </row>
     <row r="9">
@@ -588,19 +606,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E9" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F9" t="n">
-        <v>171</v>
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>162</v>
       </c>
     </row>
     <row r="10">
@@ -610,19 +631,22 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>486</v>
+        <v>461</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>435</v>
+        <v>380</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>451</v>
+        <v>498</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>235</v>
+        <v>212</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1607</v>
+        <v>393</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>1944</v>
       </c>
     </row>
     <row r="11"/>
@@ -655,7 +679,8 @@
           <t>4 bed</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr"/>
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>All</t>
         </is>
@@ -679,7 +704,7 @@
       <c r="E14" t="n">
         <v>18</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>178</v>
       </c>
     </row>
@@ -690,19 +715,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E15" t="n">
         <v>18</v>
       </c>
-      <c r="F15" t="n">
-        <v>171</v>
+      <c r="G15" t="n">
+        <v>162</v>
       </c>
     </row>
     <row r="16">
